--- a/idecba/shoppings.xlsx
+++ b/idecba/shoppings.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="56">
   <si>
     <t>Período</t>
   </si>
@@ -302,7 +302,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>). Ciudad de Buenos Aires. Enero 2014/febrero 2026</t>
+      <t>). Ciudad de Buenos Aires. Enero 2014/marzo 2026</t>
     </r>
   </si>
 </sst>
@@ -1104,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:L180"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1"/>
@@ -1132,7 +1132,7 @@
       <c r="J1" s="37"/>
       <c r="K1" s="37"/>
     </row>
-    <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="38"/>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -6707,72 +6707,94 @@
       </c>
     </row>
     <row r="163" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A163" s="23" t="s">
+      <c r="A163" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B163" s="30">
+      <c r="B163" s="35">
         <v>9.4242627999750805</v>
       </c>
-      <c r="C163" s="30">
+      <c r="C163" s="35">
         <v>15.087059446122474</v>
       </c>
-      <c r="D163" s="30">
+      <c r="D163" s="35">
         <v>82.226334583928832</v>
       </c>
-      <c r="E163" s="30">
+      <c r="E163" s="35">
         <v>-2.5256476319319376</v>
       </c>
-      <c r="F163" s="30">
+      <c r="F163" s="35">
         <v>-29.217457484690247</v>
       </c>
-      <c r="G163" s="30">
+      <c r="G163" s="35">
         <v>2.5841162234958137</v>
       </c>
-      <c r="H163" s="30">
+      <c r="H163" s="35">
         <v>-4.8083007609946771</v>
       </c>
-      <c r="I163" s="30">
+      <c r="I163" s="35">
         <v>-10.605643197174896</v>
       </c>
-      <c r="J163" s="30">
+      <c r="J163" s="35">
         <v>12.971969168889652</v>
       </c>
-      <c r="K163" s="30">
+      <c r="K163" s="35">
         <v>-11.877993018855948</v>
       </c>
     </row>
     <row r="164" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A164" s="24" t="s">
+      <c r="A164" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" s="30">
+        <v>-5.7864076956359201</v>
+      </c>
+      <c r="C164" s="30">
+        <v>13.03120821205621</v>
+      </c>
+      <c r="D164" s="30">
+        <v>49.586459065204977</v>
+      </c>
+      <c r="E164" s="30">
+        <v>-12.647514694402096</v>
+      </c>
+      <c r="F164" s="30">
+        <v>-7.9963659075643516</v>
+      </c>
+      <c r="G164" s="30">
+        <v>-16.261321850888866</v>
+      </c>
+      <c r="H164" s="30">
+        <v>-12.850029289597153</v>
+      </c>
+      <c r="I164" s="30">
+        <v>-26.070788048308525</v>
+      </c>
+      <c r="J164" s="30">
+        <v>2.8436331589110075</v>
+      </c>
+      <c r="K164" s="30">
+        <v>-19.44505267367812</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A165" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B164" s="25"/>
-      <c r="C164" s="25"/>
-      <c r="D164" s="25"/>
-      <c r="E164" s="21"/>
-      <c r="F164" s="21"/>
-      <c r="G164" s="21"/>
-      <c r="H164" s="21"/>
-      <c r="I164" s="21"/>
-      <c r="J164" s="21"/>
-      <c r="K164" s="21"/>
-    </row>
-    <row r="165" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="42" t="s">
+      <c r="B165" s="25"/>
+      <c r="C165" s="25"/>
+      <c r="D165" s="25"/>
+      <c r="E165" s="21"/>
+      <c r="F165" s="21"/>
+      <c r="G165" s="21"/>
+      <c r="H165" s="21"/>
+      <c r="I165" s="21"/>
+      <c r="J165" s="21"/>
+      <c r="K165" s="21"/>
+    </row>
+    <row r="166" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="B165" s="42"/>
-      <c r="C165" s="42"/>
-      <c r="D165" s="42"/>
-      <c r="E165" s="42"/>
-      <c r="F165" s="42"/>
-      <c r="G165" s="42"/>
-      <c r="H165" s="42"/>
-      <c r="I165" s="42"/>
-      <c r="J165" s="42"/>
-      <c r="K165" s="42"/>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A166" s="42"/>
       <c r="B166" s="42"/>
       <c r="C166" s="42"/>
       <c r="D166" s="42"/>
@@ -6784,17 +6806,18 @@
       <c r="J166" s="42"/>
       <c r="K166" s="42"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
-      <c r="E174" s="1"/>
-      <c r="F174" s="1"/>
-      <c r="G174" s="1"/>
-      <c r="H174" s="1"/>
-      <c r="I174" s="1"/>
-      <c r="J174" s="1"/>
-      <c r="K174" s="1"/>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A167" s="42"/>
+      <c r="B167" s="42"/>
+      <c r="C167" s="42"/>
+      <c r="D167" s="42"/>
+      <c r="E167" s="42"/>
+      <c r="F167" s="42"/>
+      <c r="G167" s="42"/>
+      <c r="H167" s="42"/>
+      <c r="I167" s="42"/>
+      <c r="J167" s="42"/>
+      <c r="K167" s="42"/>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B175" s="1"/>
@@ -6856,12 +6879,24 @@
       <c r="J179" s="1"/>
       <c r="K179" s="1"/>
     </row>
+    <row r="180" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+      <c r="G180" s="1"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+      <c r="J180" s="1"/>
+      <c r="K180" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A165:K166"/>
+    <mergeCell ref="A166:K167"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6897,7 +6932,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>

--- a/idecba/shoppings.xlsx
+++ b/idecba/shoppings.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="56">
   <si>
     <t>Período</t>
   </si>
@@ -302,7 +302,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>). Ciudad de Buenos Aires. Enero 2014/marzo 2026</t>
+      <t>). Ciudad de Buenos Aires. Enero 2014/abril 2026</t>
     </r>
   </si>
 </sst>
@@ -1104,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1"/>
@@ -1132,7 +1132,7 @@
       <c r="J1" s="37"/>
       <c r="K1" s="37"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="38"/>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -6742,72 +6742,94 @@
       </c>
     </row>
     <row r="164" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A164" s="23" t="s">
+      <c r="A164" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B164" s="30">
+      <c r="B164" s="35">
         <v>-5.7864076956359201</v>
       </c>
-      <c r="C164" s="30">
+      <c r="C164" s="35">
         <v>13.03120821205621</v>
       </c>
-      <c r="D164" s="30">
+      <c r="D164" s="35">
         <v>49.586459065204977</v>
       </c>
-      <c r="E164" s="30">
+      <c r="E164" s="35">
         <v>-12.647514694402096</v>
       </c>
-      <c r="F164" s="30">
+      <c r="F164" s="35">
         <v>-7.9963659075643516</v>
       </c>
-      <c r="G164" s="30">
+      <c r="G164" s="35">
         <v>-16.261321850888866</v>
       </c>
-      <c r="H164" s="30">
+      <c r="H164" s="35">
         <v>-12.850029289597153</v>
       </c>
-      <c r="I164" s="30">
+      <c r="I164" s="35">
         <v>-26.070788048308525</v>
       </c>
-      <c r="J164" s="30">
+      <c r="J164" s="35">
         <v>2.8436331589110075</v>
       </c>
-      <c r="K164" s="30">
+      <c r="K164" s="35">
         <v>-19.44505267367812</v>
       </c>
     </row>
     <row r="165" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A165" s="24" t="s">
+      <c r="A165" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" s="30">
+        <v>2.0235334275078953</v>
+      </c>
+      <c r="C165" s="30">
+        <v>20.11965277380332</v>
+      </c>
+      <c r="D165" s="30">
+        <v>84.989757124455181</v>
+      </c>
+      <c r="E165" s="30">
+        <v>-3.037364617633953</v>
+      </c>
+      <c r="F165" s="30">
+        <v>-22.882113478593769</v>
+      </c>
+      <c r="G165" s="30">
+        <v>-8.4969622772096738</v>
+      </c>
+      <c r="H165" s="30">
+        <v>-3.3087069110345202</v>
+      </c>
+      <c r="I165" s="30">
+        <v>-5.8094340275673062</v>
+      </c>
+      <c r="J165" s="30">
+        <v>8.3484741385152041</v>
+      </c>
+      <c r="K165" s="30">
+        <v>-10.553779332907276</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A166" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B165" s="25"/>
-      <c r="C165" s="25"/>
-      <c r="D165" s="25"/>
-      <c r="E165" s="21"/>
-      <c r="F165" s="21"/>
-      <c r="G165" s="21"/>
-      <c r="H165" s="21"/>
-      <c r="I165" s="21"/>
-      <c r="J165" s="21"/>
-      <c r="K165" s="21"/>
-    </row>
-    <row r="166" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="42" t="s">
+      <c r="B166" s="25"/>
+      <c r="C166" s="25"/>
+      <c r="D166" s="25"/>
+      <c r="E166" s="21"/>
+      <c r="F166" s="21"/>
+      <c r="G166" s="21"/>
+      <c r="H166" s="21"/>
+      <c r="I166" s="21"/>
+      <c r="J166" s="21"/>
+      <c r="K166" s="21"/>
+    </row>
+    <row r="167" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="B166" s="42"/>
-      <c r="C166" s="42"/>
-      <c r="D166" s="42"/>
-      <c r="E166" s="42"/>
-      <c r="F166" s="42"/>
-      <c r="G166" s="42"/>
-      <c r="H166" s="42"/>
-      <c r="I166" s="42"/>
-      <c r="J166" s="42"/>
-      <c r="K166" s="42"/>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A167" s="42"/>
       <c r="B167" s="42"/>
       <c r="C167" s="42"/>
       <c r="D167" s="42"/>
@@ -6819,17 +6841,18 @@
       <c r="J167" s="42"/>
       <c r="K167" s="42"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
-      <c r="E175" s="1"/>
-      <c r="F175" s="1"/>
-      <c r="G175" s="1"/>
-      <c r="H175" s="1"/>
-      <c r="I175" s="1"/>
-      <c r="J175" s="1"/>
-      <c r="K175" s="1"/>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A168" s="42"/>
+      <c r="B168" s="42"/>
+      <c r="C168" s="42"/>
+      <c r="D168" s="42"/>
+      <c r="E168" s="42"/>
+      <c r="F168" s="42"/>
+      <c r="G168" s="42"/>
+      <c r="H168" s="42"/>
+      <c r="I168" s="42"/>
+      <c r="J168" s="42"/>
+      <c r="K168" s="42"/>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B176" s="1"/>
@@ -6891,12 +6914,24 @@
       <c r="J180" s="1"/>
       <c r="K180" s="1"/>
     </row>
+    <row r="181" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+      <c r="G181" s="1"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="K181" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A166:K167"/>
+    <mergeCell ref="A167:K168"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6924,7 +6959,7 @@
       </c>
       <c r="B1" s="44"/>
     </row>
-    <row r="2" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
@@ -6932,7 +6967,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -6972,7 +7007,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>37</v>
       </c>
@@ -7055,7 +7090,7 @@
       <c r="A19" s="46"/>
       <c r="B19" s="49"/>
     </row>
-    <row r="20" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="47"/>
       <c r="B20" s="50"/>
     </row>

--- a/idecba/shoppings.xlsx
+++ b/idecba/shoppings.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr autoCompressPictures="0"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\CENTROS DE COMPRAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.32.3.50\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\CENTROS DE COMPRAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5299686D-A9FC-40D6-B614-E2E7F49CE0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AC_CC_AX07" sheetId="1" r:id="rId1"/>
     <sheet name="Ficha Técnica " sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="56">
   <si>
     <t>Período</t>
   </si>
@@ -302,14 +303,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>). Ciudad de Buenos Aires. Enero 2014/abril 2026</t>
+      <t>). Ciudad de Buenos Aires. Enero 2014/mayo 2026</t>
     </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -670,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -743,11 +744,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1103,67 +1099,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L182"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="1"/>
-    <col min="2" max="2" width="11.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.625" style="5"/>
-    <col min="4" max="4" width="13.125" style="5" customWidth="1"/>
-    <col min="5" max="8" width="10.625" style="5"/>
+    <col min="1" max="1" width="10.59765625" style="1"/>
+    <col min="2" max="2" width="11.59765625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10.59765625" style="5"/>
+    <col min="4" max="4" width="13.09765625" style="5" customWidth="1"/>
+    <col min="5" max="8" width="10.59765625" style="5"/>
     <col min="9" max="9" width="12" style="5" customWidth="1"/>
-    <col min="10" max="11" width="10.625" style="5"/>
-    <col min="12" max="16384" width="10.625" style="1"/>
+    <col min="10" max="11" width="10.59765625" style="5"/>
+    <col min="12" max="16384" width="10.59765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" ht="45.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="37"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1195,7 +1191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2014</v>
       </c>
@@ -1230,7 +1226,7 @@
         <v>7.4336621734070407</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1265,7 +1261,7 @@
         <v>21.061036193164639</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1300,7 +1296,7 @@
         <v>14.994864411075447</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1335,7 +1331,7 @@
         <v>1.2796494305797212</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1370,7 +1366,7 @@
         <v>21.700847771337827</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1405,7 +1401,7 @@
         <v>14.209867895728134</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1440,7 +1436,7 @@
         <v>9.8026334292617534</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1475,7 +1471,7 @@
         <v>-0.97678260020657159</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1510,7 +1506,7 @@
         <v>4.3998528656826075</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1545,7 +1541,7 @@
         <v>20.889176970783939</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1580,7 +1576,7 @@
         <v>6.1629012096927838</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1615,7 +1611,7 @@
         <v>-11.982156380136654</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -1650,7 +1646,7 @@
         <v>2.9602686764723884</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>2015</v>
       </c>
@@ -1685,7 +1681,7 @@
         <v>12.154533530106093</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
@@ -1720,7 +1716,7 @@
         <v>14.179489893716934</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
@@ -1755,7 +1751,7 @@
         <v>11.322012850041974</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
@@ -1790,7 +1786,7 @@
         <v>24.193415761793791</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
@@ -1825,7 +1821,7 @@
         <v>6.1949611576043395</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -1860,7 +1856,7 @@
         <v>10.560033339386731</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
@@ -1895,7 +1891,7 @@
         <v>-2.1240266695622623</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>18</v>
       </c>
@@ -1930,7 +1926,7 @@
         <v>15.756086467756614</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -1965,7 +1961,7 @@
         <v>11.13788141349068</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -2000,7 +1996,7 @@
         <v>8.5786056915493347</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
@@ -2035,7 +2031,7 @@
         <v>16.534199553634377</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -2070,7 +2066,7 @@
         <v>28.763556090743236</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>23</v>
       </c>
@@ -2105,7 +2101,7 @@
         <v>6.2521753576423089</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>2016</v>
       </c>
@@ -2140,7 +2136,7 @@
         <v>-17.985631612498754</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2175,7 +2171,7 @@
         <v>-0.29984684265277339</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
@@ -2210,7 +2206,7 @@
         <v>-8.1610867649421834</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
@@ -2245,7 +2241,7 @@
         <v>-7.4141425561528251</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>15</v>
       </c>
@@ -2280,7 +2276,7 @@
         <v>-10.215453076306137</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>16</v>
       </c>
@@ -2315,7 +2311,7 @@
         <v>-21.831167899767756</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>17</v>
       </c>
@@ -2350,7 +2346,7 @@
         <v>-18.1720510331557</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>18</v>
       </c>
@@ -2385,7 +2381,7 @@
         <v>-13.965363309597445</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>19</v>
       </c>
@@ -2420,7 +2416,7 @@
         <v>-15.096198125059857</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>20</v>
       </c>
@@ -2455,7 +2451,7 @@
         <v>-30.06399857904881</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>21</v>
       </c>
@@ -2490,7 +2486,7 @@
         <v>-32.119487507518741</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>22</v>
       </c>
@@ -2525,7 +2521,7 @@
         <v>-34.325981123404326</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>23</v>
       </c>
@@ -2560,7 +2556,7 @@
         <v>-14.714438190800848</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>2017</v>
       </c>
@@ -2595,7 +2591,7 @@
         <v>2.1701889094008608</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2630,7 +2626,7 @@
         <v>-19.15854141391825</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>13</v>
       </c>
@@ -2665,7 +2661,7 @@
         <v>-18.721127787059366</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -2700,7 +2696,7 @@
         <v>-20.888530998337508</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>15</v>
       </c>
@@ -2735,7 +2731,7 @@
         <v>1.8787234449736623</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>16</v>
       </c>
@@ -2770,7 +2766,7 @@
         <v>7.9125684207636438</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>17</v>
       </c>
@@ -2805,7 +2801,7 @@
         <v>9.2220104665547087</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>18</v>
       </c>
@@ -2840,7 +2836,7 @@
         <v>9.3373326069672302</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>19</v>
       </c>
@@ -2875,7 +2871,7 @@
         <v>1.4946541011374936</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>20</v>
       </c>
@@ -2910,7 +2906,7 @@
         <v>16.581696287097646</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>21</v>
       </c>
@@ -2945,7 +2941,7 @@
         <v>16.485116496669395</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>22</v>
       </c>
@@ -2980,7 +2976,7 @@
         <v>22.617670706425329</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>23</v>
       </c>
@@ -3015,7 +3011,7 @@
         <v>4.9010030335855381</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>2018</v>
       </c>
@@ -3050,7 +3046,7 @@
         <v>3.6517520350380472</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -3085,7 +3081,7 @@
         <v>21.001184868083243</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>13</v>
       </c>
@@ -3120,7 +3116,7 @@
         <v>22.010258007544948</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>14</v>
       </c>
@@ -3155,7 +3151,7 @@
         <v>28.175953249018558</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>15</v>
       </c>
@@ -3190,7 +3186,7 @@
         <v>9.9381299011922941</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>16</v>
       </c>
@@ -3225,7 +3221,7 @@
         <v>12.295734975496831</v>
       </c>
     </row>
-    <row r="63" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>17</v>
       </c>
@@ -3260,7 +3256,7 @@
         <v>7.6038156103175991</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>18</v>
       </c>
@@ -3295,7 +3291,7 @@
         <v>11.843397497356056</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>19</v>
       </c>
@@ -3330,7 +3326,7 @@
         <v>10.265120259811344</v>
       </c>
     </row>
-    <row r="66" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>20</v>
       </c>
@@ -3365,7 +3361,7 @@
         <v>14.19383640919083</v>
       </c>
     </row>
-    <row r="67" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>21</v>
       </c>
@@ -3400,7 +3396,7 @@
         <v>-4.9955358686250895</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>22</v>
       </c>
@@ -3435,7 +3431,7 @@
         <v>-3.0048340543935015</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>23</v>
       </c>
@@ -3470,7 +3466,7 @@
         <v>-0.4251839682408165</v>
       </c>
     </row>
-    <row r="70" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>2019</v>
       </c>
@@ -3505,7 +3501,7 @@
         <v>6.7973992222679636</v>
       </c>
     </row>
-    <row r="71" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
@@ -3540,7 +3536,7 @@
         <v>-3.4155588168259809</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>13</v>
       </c>
@@ -3575,7 +3571,7 @@
         <v>1.4676266243014879</v>
       </c>
     </row>
-    <row r="73" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>14</v>
       </c>
@@ -3610,7 +3606,7 @@
         <v>-0.40495990071401922</v>
       </c>
     </row>
-    <row r="74" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>15</v>
       </c>
@@ -3645,7 +3641,7 @@
         <v>-3.3373810713154373</v>
       </c>
     </row>
-    <row r="75" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>16</v>
       </c>
@@ -3680,7 +3676,7 @@
         <v>54.70222204353783</v>
       </c>
     </row>
-    <row r="76" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>17</v>
       </c>
@@ -3715,7 +3711,7 @@
         <v>2.6053507305593415</v>
       </c>
     </row>
-    <row r="77" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>18</v>
       </c>
@@ -3750,7 +3746,7 @@
         <v>-3.7341386793079745</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>19</v>
       </c>
@@ -3785,7 +3781,7 @@
         <v>8.6369961395594821</v>
       </c>
     </row>
-    <row r="79" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>20</v>
       </c>
@@ -3820,7 +3816,7 @@
         <v>4.0250525244613478</v>
       </c>
     </row>
-    <row r="80" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>21</v>
       </c>
@@ -3855,7 +3851,7 @@
         <v>29.201942289449121</v>
       </c>
     </row>
-    <row r="81" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>22</v>
       </c>
@@ -3890,7 +3886,7 @@
         <v>22.03202357022025</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>23</v>
       </c>
@@ -3925,7 +3921,7 @@
         <v>22.518877045368789</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>2020</v>
       </c>
@@ -3961,7 +3957,7 @@
       </c>
       <c r="L83" s="28"/>
     </row>
-    <row r="84" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>12</v>
       </c>
@@ -3996,7 +3992,7 @@
         <v>27.987905822643057</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>13</v>
       </c>
@@ -4031,7 +4027,7 @@
         <v>34.847282022063084</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>14</v>
       </c>
@@ -4066,7 +4062,7 @@
         <v>-28.261415202526852</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>15</v>
       </c>
@@ -4101,7 +4097,7 @@
         <v>-83.968547340466372</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>16</v>
       </c>
@@ -4136,7 +4132,7 @@
         <v>-98.691907211956675</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>24</v>
       </c>
@@ -4171,7 +4167,7 @@
         <v>-96.946439007319469</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>18</v>
       </c>
@@ -4206,7 +4202,7 @@
         <v>-96.723643104366303</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>19</v>
       </c>
@@ -4241,7 +4237,7 @@
         <v>-95.621508285672434</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>20</v>
       </c>
@@ -4276,7 +4272,7 @@
         <v>-93.563160129762352</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>21</v>
       </c>
@@ -4311,7 +4307,7 @@
         <v>-56.584104178555684</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>22</v>
       </c>
@@ -4346,7 +4342,7 @@
         <v>-36.1074001785787</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>23</v>
       </c>
@@ -4381,7 +4377,7 @@
         <v>-31.788066570966755</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A96" s="20">
         <v>2021</v>
       </c>
@@ -4416,7 +4412,7 @@
         <v>87.430321011872152</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -4451,7 +4447,7 @@
         <v>-31.945266946798935</v>
       </c>
     </row>
-    <row r="98" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>13</v>
       </c>
@@ -4486,7 +4482,7 @@
         <v>-28.38650818968398</v>
       </c>
     </row>
-    <row r="99" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>14</v>
       </c>
@@ -4521,7 +4517,7 @@
         <v>35.275700261515674</v>
       </c>
     </row>
-    <row r="100" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>15</v>
       </c>
@@ -4556,7 +4552,7 @@
         <v>284.59888537806034</v>
       </c>
     </row>
-    <row r="101" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>16</v>
       </c>
@@ -4591,7 +4587,7 @@
         <v>208.29145894640121</v>
       </c>
     </row>
-    <row r="102" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>17</v>
       </c>
@@ -4626,7 +4622,7 @@
         <v>1917.4157442359881</v>
       </c>
     </row>
-    <row r="103" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>18</v>
       </c>
@@ -4661,7 +4657,7 @@
         <v>2574.0725026544687</v>
       </c>
     </row>
-    <row r="104" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>19</v>
       </c>
@@ -4696,7 +4692,7 @@
         <v>1833.5196823196811</v>
       </c>
     </row>
-    <row r="105" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>20</v>
       </c>
@@ -4731,7 +4727,7 @@
         <v>1316.8543611275472</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>21</v>
       </c>
@@ -4766,7 +4762,7 @@
         <v>112.414031570734</v>
       </c>
     </row>
-    <row r="107" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>22</v>
       </c>
@@ -4801,7 +4797,7 @@
         <v>52.448863937215997</v>
       </c>
     </row>
-    <row r="108" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>23</v>
       </c>
@@ -4836,7 +4832,7 @@
         <v>68.385696458043043</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>2022</v>
       </c>
@@ -4871,7 +4867,7 @@
         <v>56.067699257025772</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>12</v>
       </c>
@@ -4906,7 +4902,7 @@
         <v>43.503007580624129</v>
       </c>
     </row>
-    <row r="111" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>13</v>
       </c>
@@ -4941,7 +4937,7 @@
         <v>45.281919897819023</v>
       </c>
     </row>
-    <row r="112" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>14</v>
       </c>
@@ -4976,7 +4972,7 @@
         <v>29.083806298764191</v>
       </c>
     </row>
-    <row r="113" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>15</v>
       </c>
@@ -5011,7 +5007,7 @@
         <v>115.57073600630167</v>
       </c>
     </row>
-    <row r="114" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>16</v>
       </c>
@@ -5046,7 +5042,7 @@
         <v>1919.8932886146356</v>
       </c>
     </row>
-    <row r="115" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>17</v>
       </c>
@@ -5081,7 +5077,7 @@
         <v>103.11709382182039</v>
       </c>
     </row>
-    <row r="116" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>18</v>
       </c>
@@ -5116,7 +5112,7 @@
         <v>62.974551917267533</v>
       </c>
     </row>
-    <row r="117" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>19</v>
       </c>
@@ -5151,7 +5147,7 @@
         <v>45.77474840351978</v>
       </c>
     </row>
-    <row r="118" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>20</v>
       </c>
@@ -5186,7 +5182,7 @@
         <v>33.315994070970369</v>
       </c>
     </row>
-    <row r="119" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>21</v>
       </c>
@@ -5221,7 +5217,7 @@
         <v>31.320622100687512</v>
       </c>
     </row>
-    <row r="120" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>22</v>
       </c>
@@ -5256,7 +5252,7 @@
         <v>24.517755297734634</v>
       </c>
     </row>
-    <row r="121" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>23</v>
       </c>
@@ -5291,7 +5287,7 @@
         <v>-4.3137702244226865</v>
       </c>
     </row>
-    <row r="122" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>2023</v>
       </c>
@@ -5326,7 +5322,7 @@
         <v>4.1699658104390247</v>
       </c>
     </row>
-    <row r="123" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>12</v>
       </c>
@@ -5361,7 +5357,7 @@
         <v>14.356352690923945</v>
       </c>
     </row>
-    <row r="124" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>13</v>
       </c>
@@ -5396,7 +5392,7 @@
         <v>-3.3610967339273268</v>
       </c>
     </row>
-    <row r="125" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>14</v>
       </c>
@@ -5431,7 +5427,7 @@
         <v>9.3732184262386617</v>
       </c>
     </row>
-    <row r="126" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>15</v>
       </c>
@@ -5466,7 +5462,7 @@
         <v>10.154759113499878</v>
       </c>
     </row>
-    <row r="127" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>16</v>
       </c>
@@ -5501,7 +5497,7 @@
         <v>19.491424675091551</v>
       </c>
     </row>
-    <row r="128" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>17</v>
       </c>
@@ -5536,7 +5532,7 @@
         <v>20.85802919534747</v>
       </c>
     </row>
-    <row r="129" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>18</v>
       </c>
@@ -5571,7 +5567,7 @@
         <v>14.050746234303402</v>
       </c>
     </row>
-    <row r="130" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>19</v>
       </c>
@@ -5606,7 +5602,7 @@
         <v>17.934588768948267</v>
       </c>
     </row>
-    <row r="131" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>20</v>
       </c>
@@ -5641,7 +5637,7 @@
         <v>23.818157743248115</v>
       </c>
     </row>
-    <row r="132" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>21</v>
       </c>
@@ -5676,7 +5672,7 @@
         <v>26.512655735497038</v>
       </c>
     </row>
-    <row r="133" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>22</v>
       </c>
@@ -5711,7 +5707,7 @@
         <v>27.634675140569609</v>
       </c>
     </row>
-    <row r="134" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>23</v>
       </c>
@@ -5746,7 +5742,7 @@
         <v>15.658434700802836</v>
       </c>
     </row>
-    <row r="135" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>2024</v>
       </c>
@@ -5781,7 +5777,7 @@
         <v>-16.678204100763683</v>
       </c>
     </row>
-    <row r="136" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>12</v>
       </c>
@@ -5816,7 +5812,7 @@
         <v>-27.506945165548135</v>
       </c>
     </row>
-    <row r="137" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>13</v>
       </c>
@@ -5851,7 +5847,7 @@
         <v>-19.428594487443352</v>
       </c>
     </row>
-    <row r="138" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>14</v>
       </c>
@@ -5886,7 +5882,7 @@
         <v>-24.462133389802045</v>
       </c>
     </row>
-    <row r="139" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>15</v>
       </c>
@@ -5921,7 +5917,7 @@
         <v>-36.01096677418051</v>
       </c>
     </row>
-    <row r="140" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>16</v>
       </c>
@@ -5956,7 +5952,7 @@
         <v>-37.815925337261824</v>
       </c>
     </row>
-    <row r="141" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>17</v>
       </c>
@@ -5991,7 +5987,7 @@
         <v>-26.590079561696879</v>
       </c>
     </row>
-    <row r="142" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>18</v>
       </c>
@@ -6026,7 +6022,7 @@
         <v>-30.727396759084215</v>
       </c>
     </row>
-    <row r="143" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>19</v>
       </c>
@@ -6061,7 +6057,7 @@
         <v>-28.934511623429803</v>
       </c>
     </row>
-    <row r="144" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>20</v>
       </c>
@@ -6096,7 +6092,7 @@
         <v>-33.970452222603022</v>
       </c>
     </row>
-    <row r="145" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>21</v>
       </c>
@@ -6131,7 +6127,7 @@
         <v>-40.652761984771544</v>
       </c>
     </row>
-    <row r="146" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>22</v>
       </c>
@@ -6166,7 +6162,7 @@
         <v>-25.809821695358405</v>
       </c>
     </row>
-    <row r="147" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>23</v>
       </c>
@@ -6201,7 +6197,7 @@
         <v>-19.986449286292153</v>
       </c>
     </row>
-    <row r="148" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>2025</v>
       </c>
@@ -6236,7 +6232,7 @@
         <v>-3.9234505626796867</v>
       </c>
     </row>
-    <row r="149" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>12</v>
       </c>
@@ -6271,7 +6267,7 @@
         <v>13.803575623435416</v>
       </c>
     </row>
-    <row r="150" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>13</v>
       </c>
@@ -6306,7 +6302,7 @@
         <v>4.9771982775025148</v>
       </c>
     </row>
-    <row r="151" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>14</v>
       </c>
@@ -6341,7 +6337,7 @@
         <v>16.935990503028584</v>
       </c>
     </row>
-    <row r="152" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>15</v>
       </c>
@@ -6376,562 +6372,531 @@
         <v>17.034002591007802</v>
       </c>
     </row>
-    <row r="153" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A153" s="34" t="s">
+    <row r="153" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A153" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B153" s="35">
+      <c r="B153" s="31">
         <v>-5.2679277078493181</v>
       </c>
-      <c r="C153" s="35">
+      <c r="C153" s="31">
         <v>-0.94953217593464201</v>
       </c>
-      <c r="D153" s="35">
+      <c r="D153" s="31">
         <v>14.91423342553977</v>
       </c>
-      <c r="E153" s="35">
+      <c r="E153" s="31">
         <v>-5.3591591102448488</v>
       </c>
-      <c r="F153" s="35">
+      <c r="F153" s="31">
         <v>39.97115383333545</v>
       </c>
-      <c r="G153" s="35">
+      <c r="G153" s="31">
         <v>31.363770046330263</v>
       </c>
-      <c r="H153" s="35">
+      <c r="H153" s="31">
         <v>12.913235956302049</v>
       </c>
-      <c r="I153" s="35">
+      <c r="I153" s="31">
         <v>35.77405662615061</v>
       </c>
-      <c r="J153" s="35">
+      <c r="J153" s="31">
         <v>13.806817679537353</v>
       </c>
-      <c r="K153" s="35">
+      <c r="K153" s="31">
         <v>12.762661226991501</v>
       </c>
     </row>
-    <row r="154" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A154" s="34" t="s">
+    <row r="154" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A154" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B154" s="35">
+      <c r="B154" s="31">
         <v>-3.2986546503694258</v>
       </c>
-      <c r="C154" s="35">
+      <c r="C154" s="31">
         <v>-11.652473909999895</v>
       </c>
-      <c r="D154" s="35">
+      <c r="D154" s="31">
         <v>2.151883958163836</v>
       </c>
-      <c r="E154" s="35">
+      <c r="E154" s="31">
         <v>-13.896454736534491</v>
       </c>
-      <c r="F154" s="35">
+      <c r="F154" s="31">
         <v>-2.1071413459955446</v>
       </c>
-      <c r="G154" s="35">
+      <c r="G154" s="31">
         <v>10.847372557013868</v>
       </c>
-      <c r="H154" s="35">
+      <c r="H154" s="31">
         <v>-6.5511822236301693</v>
       </c>
-      <c r="I154" s="35">
+      <c r="I154" s="31">
         <v>-37.029271807395936</v>
       </c>
-      <c r="J154" s="35">
+      <c r="J154" s="31">
         <v>-4.2821435906043366</v>
       </c>
-      <c r="K154" s="35">
+      <c r="K154" s="31">
         <v>-6.6642227594659325</v>
       </c>
     </row>
-    <row r="155" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A155" s="34" t="s">
+    <row r="155" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A155" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B155" s="35">
+      <c r="B155" s="31">
         <v>-11.566009139488308</v>
       </c>
-      <c r="C155" s="35">
+      <c r="C155" s="31">
         <v>-13.281074689464912</v>
       </c>
-      <c r="D155" s="35">
+      <c r="D155" s="31">
         <v>-4.2336294695575312</v>
       </c>
-      <c r="E155" s="35">
+      <c r="E155" s="31">
         <v>-9.4806034980343679</v>
       </c>
-      <c r="F155" s="35">
+      <c r="F155" s="31">
         <v>-2.1075346661576067</v>
       </c>
-      <c r="G155" s="35">
+      <c r="G155" s="31">
         <v>10.078211517706537</v>
       </c>
-      <c r="H155" s="35">
+      <c r="H155" s="31">
         <v>-2.6793583676416155</v>
       </c>
-      <c r="I155" s="35">
+      <c r="I155" s="31">
         <v>-15.982226558974066</v>
       </c>
-      <c r="J155" s="35">
+      <c r="J155" s="31">
         <v>7.4474347656583229</v>
       </c>
-      <c r="K155" s="35">
+      <c r="K155" s="31">
         <v>-9.3263616520678827</v>
       </c>
     </row>
-    <row r="156" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A156" s="34" t="s">
+    <row r="156" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A156" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B156" s="35">
+      <c r="B156" s="31">
         <v>-9.8008200724136749</v>
       </c>
-      <c r="C156" s="35">
+      <c r="C156" s="31">
         <v>-9.4333172711993818</v>
       </c>
-      <c r="D156" s="35">
+      <c r="D156" s="31">
         <v>0.36358840184989027</v>
       </c>
-      <c r="E156" s="35">
+      <c r="E156" s="31">
         <v>-0.92540851937937818</v>
       </c>
-      <c r="F156" s="35">
+      <c r="F156" s="31">
         <v>19.774818180034039</v>
       </c>
-      <c r="G156" s="35">
+      <c r="G156" s="31">
         <v>3.8693689362545136</v>
       </c>
-      <c r="H156" s="35">
+      <c r="H156" s="31">
         <v>-8.1744626097897353</v>
       </c>
-      <c r="I156" s="35">
+      <c r="I156" s="31">
         <v>8.7490768232779672</v>
       </c>
-      <c r="J156" s="35">
+      <c r="J156" s="31">
         <v>6.8120866139343983</v>
       </c>
-      <c r="K156" s="35">
+      <c r="K156" s="31">
         <v>-14.245350789958033</v>
       </c>
     </row>
-    <row r="157" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A157" s="34" t="s">
+    <row r="157" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A157" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="35">
+      <c r="B157" s="31">
         <v>-11.527414221791311</v>
       </c>
-      <c r="C157" s="35">
+      <c r="C157" s="31">
         <v>-5.6256359591605465</v>
       </c>
-      <c r="D157" s="35">
+      <c r="D157" s="31">
         <v>42.293349302950304</v>
       </c>
-      <c r="E157" s="35">
+      <c r="E157" s="31">
         <v>-0.76832426669124487</v>
       </c>
-      <c r="F157" s="35">
+      <c r="F157" s="31">
         <v>13.155962440532477</v>
       </c>
-      <c r="G157" s="35">
+      <c r="G157" s="31">
         <v>1.5952986159927018</v>
       </c>
-      <c r="H157" s="35">
+      <c r="H157" s="31">
         <v>-8.9525564715623123</v>
       </c>
-      <c r="I157" s="35">
+      <c r="I157" s="31">
         <v>27.221329819574393</v>
       </c>
-      <c r="J157" s="35">
+      <c r="J157" s="31">
         <v>2.3003020895056236</v>
       </c>
-      <c r="K157" s="35">
+      <c r="K157" s="31">
         <v>-13.588958706756294</v>
       </c>
     </row>
-    <row r="158" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A158" s="34" t="s">
+    <row r="158" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A158" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B158" s="35">
+      <c r="B158" s="31">
         <v>-5.8618528097964084</v>
       </c>
-      <c r="C158" s="35">
+      <c r="C158" s="31">
         <v>-4.200667120847223</v>
       </c>
-      <c r="D158" s="35">
+      <c r="D158" s="31">
         <v>74.103184451131909</v>
       </c>
-      <c r="E158" s="35">
+      <c r="E158" s="31">
         <v>-1.5863746929946188</v>
       </c>
-      <c r="F158" s="35">
+      <c r="F158" s="31">
         <v>11.297860938932525</v>
       </c>
-      <c r="G158" s="35">
+      <c r="G158" s="31">
         <v>2.0567991335282532</v>
       </c>
-      <c r="H158" s="35">
+      <c r="H158" s="31">
         <v>-1.5641044156876949</v>
       </c>
-      <c r="I158" s="35">
+      <c r="I158" s="31">
         <v>-26.184698079517808</v>
       </c>
-      <c r="J158" s="35">
+      <c r="J158" s="31">
         <v>0.7745959307488004</v>
       </c>
-      <c r="K158" s="35">
+      <c r="K158" s="31">
         <v>-5.9948136103240124</v>
       </c>
     </row>
-    <row r="159" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A159" s="34" t="s">
+    <row r="159" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A159" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B159" s="35">
+      <c r="B159" s="31">
         <v>3.7322578622188685</v>
       </c>
-      <c r="C159" s="35">
+      <c r="C159" s="31">
         <v>-3.418901828971832</v>
       </c>
-      <c r="D159" s="35">
+      <c r="D159" s="31">
         <v>66.786442236362802</v>
       </c>
-      <c r="E159" s="35">
+      <c r="E159" s="31">
         <v>-0.23592275475184943</v>
       </c>
-      <c r="F159" s="35">
+      <c r="F159" s="31">
         <v>0.45167282749771775</v>
       </c>
-      <c r="G159" s="35">
+      <c r="G159" s="31">
         <v>3.3968381850322471</v>
       </c>
-      <c r="H159" s="35">
+      <c r="H159" s="31">
         <v>4.6097595539379199</v>
       </c>
-      <c r="I159" s="35">
+      <c r="I159" s="31">
         <v>-27.168516587815429</v>
       </c>
-      <c r="J159" s="35">
+      <c r="J159" s="31">
         <v>11.008508868558909</v>
       </c>
-      <c r="K159" s="35">
+      <c r="K159" s="31">
         <v>-19.14810650609612</v>
       </c>
     </row>
-    <row r="160" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A160" s="34" t="s">
+    <row r="160" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A160" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B160" s="35">
+      <c r="B160" s="31">
         <v>2.0858642426762053</v>
       </c>
-      <c r="C160" s="35">
+      <c r="C160" s="31">
         <v>-4.8233816782494721E-2</v>
       </c>
-      <c r="D160" s="35">
+      <c r="D160" s="31">
         <v>49.781527723605222</v>
       </c>
-      <c r="E160" s="35">
+      <c r="E160" s="31">
         <v>-4.8807095410255741</v>
       </c>
-      <c r="F160" s="35">
+      <c r="F160" s="31">
         <v>1.2355301806196151</v>
       </c>
-      <c r="G160" s="35">
+      <c r="G160" s="31">
         <v>-4.4032604527998176</v>
       </c>
-      <c r="H160" s="35">
+      <c r="H160" s="31">
         <v>-6.3443391169110903</v>
       </c>
-      <c r="I160" s="35">
+      <c r="I160" s="31">
         <v>-13.622710048909681</v>
       </c>
-      <c r="J160" s="35">
+      <c r="J160" s="31">
         <v>0.19955457853402248</v>
       </c>
-      <c r="K160" s="35">
+      <c r="K160" s="31">
         <v>-17.575346128292491</v>
       </c>
     </row>
-    <row r="161" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A161" s="36">
+    <row r="161" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A161" s="4">
         <v>2026</v>
       </c>
-      <c r="B161" s="35"/>
-      <c r="C161" s="35"/>
-      <c r="D161" s="35"/>
-      <c r="E161" s="35"/>
-      <c r="F161" s="35"/>
-      <c r="G161" s="35"/>
-      <c r="H161" s="35"/>
-      <c r="I161" s="35"/>
-      <c r="J161" s="35"/>
-      <c r="K161" s="35"/>
-    </row>
-    <row r="162" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A162" s="34" t="s">
+      <c r="B161" s="31"/>
+      <c r="C161" s="31"/>
+      <c r="D161" s="31"/>
+      <c r="E161" s="31"/>
+      <c r="F161" s="31"/>
+      <c r="G161" s="31"/>
+      <c r="H161" s="31"/>
+      <c r="I161" s="31"/>
+      <c r="J161" s="31"/>
+      <c r="K161" s="31"/>
+    </row>
+    <row r="162" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A162" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B162" s="35">
+      <c r="B162" s="31">
         <v>5.8152767443154119</v>
       </c>
-      <c r="C162" s="35">
+      <c r="C162" s="31">
         <v>2.4498586865609795</v>
       </c>
-      <c r="D162" s="35">
+      <c r="D162" s="31">
         <v>91.524913635223839</v>
       </c>
-      <c r="E162" s="35">
+      <c r="E162" s="31">
         <v>-4.1160047797977439</v>
       </c>
-      <c r="F162" s="35">
+      <c r="F162" s="31">
         <v>-3.1818121272530031</v>
       </c>
-      <c r="G162" s="35">
+      <c r="G162" s="31">
         <v>-2.8218505811684613</v>
       </c>
-      <c r="H162" s="35">
+      <c r="H162" s="31">
         <v>-3.5425625618972112</v>
       </c>
-      <c r="I162" s="35">
+      <c r="I162" s="31">
         <v>-17.840478586072539</v>
       </c>
-      <c r="J162" s="35">
+      <c r="J162" s="31">
         <v>14.857863616393786</v>
       </c>
-      <c r="K162" s="35">
+      <c r="K162" s="31">
         <v>-10.78053091076595</v>
       </c>
     </row>
-    <row r="163" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A163" s="34" t="s">
+    <row r="163" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A163" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B163" s="35">
+      <c r="B163" s="31">
         <v>9.4242627999750805</v>
       </c>
-      <c r="C163" s="35">
+      <c r="C163" s="31">
         <v>15.087059446122474</v>
       </c>
-      <c r="D163" s="35">
+      <c r="D163" s="31">
         <v>82.226334583928832</v>
       </c>
-      <c r="E163" s="35">
+      <c r="E163" s="31">
         <v>-2.5256476319319376</v>
       </c>
-      <c r="F163" s="35">
+      <c r="F163" s="31">
         <v>-29.217457484690247</v>
       </c>
-      <c r="G163" s="35">
+      <c r="G163" s="31">
         <v>2.5841162234958137</v>
       </c>
-      <c r="H163" s="35">
+      <c r="H163" s="31">
         <v>-4.8083007609946771</v>
       </c>
-      <c r="I163" s="35">
+      <c r="I163" s="31">
         <v>-10.605643197174896</v>
       </c>
-      <c r="J163" s="35">
+      <c r="J163" s="31">
         <v>12.971969168889652</v>
       </c>
-      <c r="K163" s="35">
+      <c r="K163" s="31">
         <v>-11.877993018855948</v>
       </c>
     </row>
-    <row r="164" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A164" s="34" t="s">
+    <row r="164" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A164" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B164" s="35">
+      <c r="B164" s="31">
         <v>-5.7864076956359201</v>
       </c>
-      <c r="C164" s="35">
+      <c r="C164" s="31">
         <v>13.03120821205621</v>
       </c>
-      <c r="D164" s="35">
+      <c r="D164" s="31">
         <v>49.586459065204977</v>
       </c>
-      <c r="E164" s="35">
+      <c r="E164" s="31">
         <v>-12.647514694402096</v>
       </c>
-      <c r="F164" s="35">
+      <c r="F164" s="31">
         <v>-7.9963659075643516</v>
       </c>
-      <c r="G164" s="35">
+      <c r="G164" s="31">
         <v>-16.261321850888866</v>
       </c>
-      <c r="H164" s="35">
+      <c r="H164" s="31">
         <v>-12.850029289597153</v>
       </c>
-      <c r="I164" s="35">
+      <c r="I164" s="31">
         <v>-26.070788048308525</v>
       </c>
-      <c r="J164" s="35">
+      <c r="J164" s="31">
         <v>2.8436331589110075</v>
       </c>
-      <c r="K164" s="35">
+      <c r="K164" s="31">
         <v>-19.44505267367812</v>
       </c>
     </row>
-    <row r="165" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A165" s="23" t="s">
+    <row r="165" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A165" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B165" s="30">
+      <c r="B165" s="31">
         <v>2.0235334275078953</v>
       </c>
-      <c r="C165" s="30">
+      <c r="C165" s="31">
         <v>20.11965277380332</v>
       </c>
-      <c r="D165" s="30">
+      <c r="D165" s="31">
         <v>84.989757124455181</v>
       </c>
-      <c r="E165" s="30">
+      <c r="E165" s="31">
         <v>-3.037364617633953</v>
       </c>
-      <c r="F165" s="30">
+      <c r="F165" s="31">
         <v>-22.882113478593769</v>
       </c>
-      <c r="G165" s="30">
+      <c r="G165" s="31">
         <v>-8.4969622772096738</v>
       </c>
-      <c r="H165" s="30">
+      <c r="H165" s="31">
         <v>-3.3087069110345202</v>
       </c>
-      <c r="I165" s="30">
+      <c r="I165" s="31">
         <v>-5.8094340275673062</v>
       </c>
-      <c r="J165" s="30">
+      <c r="J165" s="31">
         <v>8.3484741385152041</v>
       </c>
-      <c r="K165" s="30">
+      <c r="K165" s="31">
         <v>-10.553779332907276</v>
       </c>
     </row>
-    <row r="166" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A166" s="24" t="s">
+    <row r="166" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A166" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B166" s="30">
+        <v>21.785776842501512</v>
+      </c>
+      <c r="C166" s="30">
+        <v>33.502499828042431</v>
+      </c>
+      <c r="D166" s="30">
+        <v>111.53185904991921</v>
+      </c>
+      <c r="E166" s="30">
+        <v>9.2022268064088095</v>
+      </c>
+      <c r="F166" s="30">
+        <v>-17.530881472698223</v>
+      </c>
+      <c r="G166" s="30">
+        <v>5.748044330821922</v>
+      </c>
+      <c r="H166" s="30">
+        <v>-8.362704000130039</v>
+      </c>
+      <c r="I166" s="30">
+        <v>-7.9607564480824511</v>
+      </c>
+      <c r="J166" s="30">
+        <v>17.552686765482694</v>
+      </c>
+      <c r="K166" s="30">
+        <v>-2.0735552481443986</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A167" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B166" s="25"/>
-      <c r="C166" s="25"/>
-      <c r="D166" s="25"/>
-      <c r="E166" s="21"/>
-      <c r="F166" s="21"/>
-      <c r="G166" s="21"/>
-      <c r="H166" s="21"/>
-      <c r="I166" s="21"/>
-      <c r="J166" s="21"/>
-      <c r="K166" s="21"/>
-    </row>
-    <row r="167" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="42" t="s">
+      <c r="B167" s="25"/>
+      <c r="C167" s="25"/>
+      <c r="D167" s="25"/>
+      <c r="E167" s="21"/>
+      <c r="F167" s="21"/>
+      <c r="G167" s="21"/>
+      <c r="H167" s="21"/>
+      <c r="I167" s="21"/>
+      <c r="J167" s="21"/>
+      <c r="K167" s="21"/>
+    </row>
+    <row r="168" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="B167" s="42"/>
-      <c r="C167" s="42"/>
-      <c r="D167" s="42"/>
-      <c r="E167" s="42"/>
-      <c r="F167" s="42"/>
-      <c r="G167" s="42"/>
-      <c r="H167" s="42"/>
-      <c r="I167" s="42"/>
-      <c r="J167" s="42"/>
-      <c r="K167" s="42"/>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A168" s="42"/>
-      <c r="B168" s="42"/>
-      <c r="C168" s="42"/>
-      <c r="D168" s="42"/>
-      <c r="E168" s="42"/>
-      <c r="F168" s="42"/>
-      <c r="G168" s="42"/>
-      <c r="H168" s="42"/>
-      <c r="I168" s="42"/>
-      <c r="J168" s="42"/>
-      <c r="K168" s="42"/>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
-      <c r="E176" s="1"/>
-      <c r="F176" s="1"/>
-      <c r="G176" s="1"/>
-      <c r="H176" s="1"/>
-      <c r="I176" s="1"/>
-      <c r="J176" s="1"/>
-      <c r="K176" s="1"/>
-    </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
-      <c r="E177" s="1"/>
-      <c r="F177" s="1"/>
-      <c r="G177" s="1"/>
-      <c r="H177" s="1"/>
-      <c r="I177" s="1"/>
-      <c r="J177" s="1"/>
-      <c r="K177" s="1"/>
-    </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
-      <c r="E178" s="1"/>
-      <c r="F178" s="1"/>
-      <c r="G178" s="1"/>
-      <c r="H178" s="1"/>
-      <c r="I178" s="1"/>
-      <c r="J178" s="1"/>
-      <c r="K178" s="1"/>
-    </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
-      <c r="E179" s="1"/>
-      <c r="F179" s="1"/>
-      <c r="G179" s="1"/>
-      <c r="H179" s="1"/>
-      <c r="I179" s="1"/>
-      <c r="J179" s="1"/>
-      <c r="K179" s="1"/>
-    </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
-      <c r="E180" s="1"/>
-      <c r="F180" s="1"/>
-      <c r="G180" s="1"/>
-      <c r="H180" s="1"/>
-      <c r="I180" s="1"/>
-      <c r="J180" s="1"/>
-      <c r="K180" s="1"/>
-    </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
-      <c r="E181" s="1"/>
-      <c r="F181" s="1"/>
-      <c r="G181" s="1"/>
-      <c r="H181" s="1"/>
-      <c r="I181" s="1"/>
-      <c r="J181" s="1"/>
-      <c r="K181" s="1"/>
-    </row>
+      <c r="B168" s="39"/>
+      <c r="C168" s="39"/>
+      <c r="D168" s="39"/>
+      <c r="E168" s="39"/>
+      <c r="F168" s="39"/>
+      <c r="G168" s="39"/>
+      <c r="H168" s="39"/>
+      <c r="I168" s="39"/>
+      <c r="J168" s="39"/>
+      <c r="K168" s="39"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" s="39"/>
+      <c r="B169" s="39"/>
+      <c r="C169" s="39"/>
+      <c r="D169" s="39"/>
+      <c r="E169" s="39"/>
+      <c r="F169" s="39"/>
+      <c r="G169" s="39"/>
+      <c r="H169" s="39"/>
+      <c r="I169" s="39"/>
+      <c r="J169" s="39"/>
+      <c r="K169" s="39"/>
+    </row>
+    <row r="177" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="178" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="179" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="180" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="181" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="182" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A167:K168"/>
+    <mergeCell ref="A168:K169"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6944,22 +6909,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="48.625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="10.625" style="6"/>
+    <col min="1" max="1" width="35.09765625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="48.59765625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="10.59765625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="44"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="41"/>
+    </row>
+    <row r="2" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
@@ -6967,7 +6932,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -6975,7 +6940,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>30</v>
       </c>
@@ -6983,7 +6948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
@@ -6991,7 +6956,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
         <v>34</v>
       </c>
@@ -6999,7 +6964,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>35</v>
       </c>
@@ -7007,7 +6972,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>37</v>
       </c>
@@ -7015,7 +6980,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
@@ -7023,7 +6988,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>39</v>
       </c>
@@ -7034,7 +6999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>41</v>
       </c>
@@ -7042,7 +7007,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>43</v>
       </c>
@@ -7050,7 +7015,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>50</v>
       </c>
@@ -7058,7 +7023,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>45</v>
       </c>
@@ -7066,33 +7031,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="45" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="45" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="46"/>
-      <c r="B16" s="49"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="46"/>
-      <c r="B17" s="49"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="46"/>
-      <c r="B18" s="49"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="46"/>
-      <c r="B19" s="49"/>
-    </row>
-    <row r="20" spans="1:2" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="50"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
+      <c r="B16" s="46"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="43"/>
+      <c r="B17" s="46"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="43"/>
+      <c r="B18" s="46"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="43"/>
+      <c r="B19" s="46"/>
+    </row>
+    <row r="20" spans="1:2" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="44"/>
+      <c r="B20" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/idecba/shoppings.xlsx
+++ b/idecba/shoppings.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr autoCompressPictures="0" defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.32.3.50\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\CENTROS DE COMPRAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5299686D-A9FC-40D6-B614-E2E7F49CE0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8505"/>
   </bookViews>
   <sheets>
     <sheet name="AC_CC_AX07" sheetId="1" r:id="rId1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="56">
   <si>
     <t>Período</t>
   </si>
@@ -303,14 +302,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>). Ciudad de Buenos Aires. Enero 2014/mayo 2026</t>
+      <t>). Ciudad de Buenos Aires. Enero 2014/junio 2026</t>
     </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -671,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -744,6 +743,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1099,67 +1103,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L182"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L183"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" style="1"/>
-    <col min="2" max="2" width="11.59765625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" style="5"/>
-    <col min="4" max="4" width="13.09765625" style="5" customWidth="1"/>
-    <col min="5" max="8" width="10.59765625" style="5"/>
+    <col min="1" max="1" width="10.625" style="1"/>
+    <col min="2" max="2" width="11.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10.625" style="5"/>
+    <col min="4" max="4" width="13.125" style="5" customWidth="1"/>
+    <col min="5" max="8" width="10.625" style="5"/>
     <col min="9" max="9" width="12" style="5" customWidth="1"/>
-    <col min="10" max="11" width="10.59765625" style="5"/>
-    <col min="12" max="16384" width="10.59765625" style="1"/>
+    <col min="10" max="11" width="10.625" style="5"/>
+    <col min="12" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" ht="45.6" x14ac:dyDescent="0.2">
-      <c r="A4" s="37"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" s="40"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1191,7 +1195,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2014</v>
       </c>
@@ -1226,7 +1230,7 @@
         <v>7.4336621734070407</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1261,7 +1265,7 @@
         <v>21.061036193164639</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1296,7 +1300,7 @@
         <v>14.994864411075447</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1331,7 +1335,7 @@
         <v>1.2796494305797212</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1366,7 +1370,7 @@
         <v>21.700847771337827</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1401,7 +1405,7 @@
         <v>14.209867895728134</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1436,7 +1440,7 @@
         <v>9.8026334292617534</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1471,7 +1475,7 @@
         <v>-0.97678260020657159</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1506,7 +1510,7 @@
         <v>4.3998528656826075</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1541,7 +1545,7 @@
         <v>20.889176970783939</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1576,7 +1580,7 @@
         <v>6.1629012096927838</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1611,7 +1615,7 @@
         <v>-11.982156380136654</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -1646,7 +1650,7 @@
         <v>2.9602686764723884</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>2015</v>
       </c>
@@ -1681,7 +1685,7 @@
         <v>12.154533530106093</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
@@ -1716,7 +1720,7 @@
         <v>14.179489893716934</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
@@ -1751,7 +1755,7 @@
         <v>11.322012850041974</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
@@ -1786,7 +1790,7 @@
         <v>24.193415761793791</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
@@ -1821,7 +1825,7 @@
         <v>6.1949611576043395</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -1856,7 +1860,7 @@
         <v>10.560033339386731</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
@@ -1891,7 +1895,7 @@
         <v>-2.1240266695622623</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>18</v>
       </c>
@@ -1926,7 +1930,7 @@
         <v>15.756086467756614</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -1961,7 +1965,7 @@
         <v>11.13788141349068</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -1996,7 +2000,7 @@
         <v>8.5786056915493347</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
@@ -2031,7 +2035,7 @@
         <v>16.534199553634377</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -2066,7 +2070,7 @@
         <v>28.763556090743236</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>23</v>
       </c>
@@ -2101,7 +2105,7 @@
         <v>6.2521753576423089</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>2016</v>
       </c>
@@ -2136,7 +2140,7 @@
         <v>-17.985631612498754</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2171,7 +2175,7 @@
         <v>-0.29984684265277339</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
@@ -2206,7 +2210,7 @@
         <v>-8.1610867649421834</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
@@ -2241,7 +2245,7 @@
         <v>-7.4141425561528251</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>15</v>
       </c>
@@ -2276,7 +2280,7 @@
         <v>-10.215453076306137</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>16</v>
       </c>
@@ -2311,7 +2315,7 @@
         <v>-21.831167899767756</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>17</v>
       </c>
@@ -2346,7 +2350,7 @@
         <v>-18.1720510331557</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>18</v>
       </c>
@@ -2381,7 +2385,7 @@
         <v>-13.965363309597445</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>19</v>
       </c>
@@ -2416,7 +2420,7 @@
         <v>-15.096198125059857</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>20</v>
       </c>
@@ -2451,7 +2455,7 @@
         <v>-30.06399857904881</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>21</v>
       </c>
@@ -2486,7 +2490,7 @@
         <v>-32.119487507518741</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>22</v>
       </c>
@@ -2521,7 +2525,7 @@
         <v>-34.325981123404326</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>23</v>
       </c>
@@ -2556,7 +2560,7 @@
         <v>-14.714438190800848</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>2017</v>
       </c>
@@ -2591,7 +2595,7 @@
         <v>2.1701889094008608</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2626,7 +2630,7 @@
         <v>-19.15854141391825</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>13</v>
       </c>
@@ -2661,7 +2665,7 @@
         <v>-18.721127787059366</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -2696,7 +2700,7 @@
         <v>-20.888530998337508</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>15</v>
       </c>
@@ -2731,7 +2735,7 @@
         <v>1.8787234449736623</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>16</v>
       </c>
@@ -2766,7 +2770,7 @@
         <v>7.9125684207636438</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>17</v>
       </c>
@@ -2801,7 +2805,7 @@
         <v>9.2220104665547087</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>18</v>
       </c>
@@ -2836,7 +2840,7 @@
         <v>9.3373326069672302</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>19</v>
       </c>
@@ -2871,7 +2875,7 @@
         <v>1.4946541011374936</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>20</v>
       </c>
@@ -2906,7 +2910,7 @@
         <v>16.581696287097646</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>21</v>
       </c>
@@ -2941,7 +2945,7 @@
         <v>16.485116496669395</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>22</v>
       </c>
@@ -2976,7 +2980,7 @@
         <v>22.617670706425329</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>23</v>
       </c>
@@ -3011,7 +3015,7 @@
         <v>4.9010030335855381</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>2018</v>
       </c>
@@ -3046,7 +3050,7 @@
         <v>3.6517520350380472</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -3081,7 +3085,7 @@
         <v>21.001184868083243</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>13</v>
       </c>
@@ -3116,7 +3120,7 @@
         <v>22.010258007544948</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>14</v>
       </c>
@@ -3151,7 +3155,7 @@
         <v>28.175953249018558</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>15</v>
       </c>
@@ -3186,7 +3190,7 @@
         <v>9.9381299011922941</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>16</v>
       </c>
@@ -3221,7 +3225,7 @@
         <v>12.295734975496831</v>
       </c>
     </row>
-    <row r="63" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>17</v>
       </c>
@@ -3256,7 +3260,7 @@
         <v>7.6038156103175991</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>18</v>
       </c>
@@ -3291,7 +3295,7 @@
         <v>11.843397497356056</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>19</v>
       </c>
@@ -3326,7 +3330,7 @@
         <v>10.265120259811344</v>
       </c>
     </row>
-    <row r="66" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>20</v>
       </c>
@@ -3361,7 +3365,7 @@
         <v>14.19383640919083</v>
       </c>
     </row>
-    <row r="67" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>21</v>
       </c>
@@ -3396,7 +3400,7 @@
         <v>-4.9955358686250895</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>22</v>
       </c>
@@ -3431,7 +3435,7 @@
         <v>-3.0048340543935015</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>23</v>
       </c>
@@ -3466,7 +3470,7 @@
         <v>-0.4251839682408165</v>
       </c>
     </row>
-    <row r="70" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>2019</v>
       </c>
@@ -3501,7 +3505,7 @@
         <v>6.7973992222679636</v>
       </c>
     </row>
-    <row r="71" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
@@ -3536,7 +3540,7 @@
         <v>-3.4155588168259809</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>13</v>
       </c>
@@ -3571,7 +3575,7 @@
         <v>1.4676266243014879</v>
       </c>
     </row>
-    <row r="73" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>14</v>
       </c>
@@ -3606,7 +3610,7 @@
         <v>-0.40495990071401922</v>
       </c>
     </row>
-    <row r="74" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>15</v>
       </c>
@@ -3641,7 +3645,7 @@
         <v>-3.3373810713154373</v>
       </c>
     </row>
-    <row r="75" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>16</v>
       </c>
@@ -3676,7 +3680,7 @@
         <v>54.70222204353783</v>
       </c>
     </row>
-    <row r="76" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>17</v>
       </c>
@@ -3711,7 +3715,7 @@
         <v>2.6053507305593415</v>
       </c>
     </row>
-    <row r="77" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>18</v>
       </c>
@@ -3746,7 +3750,7 @@
         <v>-3.7341386793079745</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>19</v>
       </c>
@@ -3781,7 +3785,7 @@
         <v>8.6369961395594821</v>
       </c>
     </row>
-    <row r="79" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>20</v>
       </c>
@@ -3816,7 +3820,7 @@
         <v>4.0250525244613478</v>
       </c>
     </row>
-    <row r="80" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>21</v>
       </c>
@@ -3851,7 +3855,7 @@
         <v>29.201942289449121</v>
       </c>
     </row>
-    <row r="81" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>22</v>
       </c>
@@ -3886,7 +3890,7 @@
         <v>22.03202357022025</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>23</v>
       </c>
@@ -3921,7 +3925,7 @@
         <v>22.518877045368789</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>2020</v>
       </c>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="L83" s="28"/>
     </row>
-    <row r="84" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>12</v>
       </c>
@@ -3992,7 +3996,7 @@
         <v>27.987905822643057</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>13</v>
       </c>
@@ -4027,7 +4031,7 @@
         <v>34.847282022063084</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>14</v>
       </c>
@@ -4062,7 +4066,7 @@
         <v>-28.261415202526852</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>15</v>
       </c>
@@ -4097,7 +4101,7 @@
         <v>-83.968547340466372</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>16</v>
       </c>
@@ -4132,7 +4136,7 @@
         <v>-98.691907211956675</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>24</v>
       </c>
@@ -4167,7 +4171,7 @@
         <v>-96.946439007319469</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>18</v>
       </c>
@@ -4202,7 +4206,7 @@
         <v>-96.723643104366303</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>19</v>
       </c>
@@ -4237,7 +4241,7 @@
         <v>-95.621508285672434</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>20</v>
       </c>
@@ -4272,7 +4276,7 @@
         <v>-93.563160129762352</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>21</v>
       </c>
@@ -4307,7 +4311,7 @@
         <v>-56.584104178555684</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>22</v>
       </c>
@@ -4342,7 +4346,7 @@
         <v>-36.1074001785787</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>23</v>
       </c>
@@ -4377,7 +4381,7 @@
         <v>-31.788066570966755</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A96" s="20">
         <v>2021</v>
       </c>
@@ -4412,7 +4416,7 @@
         <v>87.430321011872152</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -4447,7 +4451,7 @@
         <v>-31.945266946798935</v>
       </c>
     </row>
-    <row r="98" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>13</v>
       </c>
@@ -4482,7 +4486,7 @@
         <v>-28.38650818968398</v>
       </c>
     </row>
-    <row r="99" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>14</v>
       </c>
@@ -4517,7 +4521,7 @@
         <v>35.275700261515674</v>
       </c>
     </row>
-    <row r="100" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>15</v>
       </c>
@@ -4552,7 +4556,7 @@
         <v>284.59888537806034</v>
       </c>
     </row>
-    <row r="101" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>16</v>
       </c>
@@ -4587,7 +4591,7 @@
         <v>208.29145894640121</v>
       </c>
     </row>
-    <row r="102" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>17</v>
       </c>
@@ -4622,7 +4626,7 @@
         <v>1917.4157442359881</v>
       </c>
     </row>
-    <row r="103" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>18</v>
       </c>
@@ -4657,7 +4661,7 @@
         <v>2574.0725026544687</v>
       </c>
     </row>
-    <row r="104" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>19</v>
       </c>
@@ -4692,7 +4696,7 @@
         <v>1833.5196823196811</v>
       </c>
     </row>
-    <row r="105" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>20</v>
       </c>
@@ -4727,7 +4731,7 @@
         <v>1316.8543611275472</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>21</v>
       </c>
@@ -4762,7 +4766,7 @@
         <v>112.414031570734</v>
       </c>
     </row>
-    <row r="107" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>22</v>
       </c>
@@ -4797,7 +4801,7 @@
         <v>52.448863937215997</v>
       </c>
     </row>
-    <row r="108" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>23</v>
       </c>
@@ -4832,7 +4836,7 @@
         <v>68.385696458043043</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" s="27" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>2022</v>
       </c>
@@ -4867,7 +4871,7 @@
         <v>56.067699257025772</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>12</v>
       </c>
@@ -4902,7 +4906,7 @@
         <v>43.503007580624129</v>
       </c>
     </row>
-    <row r="111" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>13</v>
       </c>
@@ -4937,7 +4941,7 @@
         <v>45.281919897819023</v>
       </c>
     </row>
-    <row r="112" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>14</v>
       </c>
@@ -4972,7 +4976,7 @@
         <v>29.083806298764191</v>
       </c>
     </row>
-    <row r="113" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>15</v>
       </c>
@@ -5007,7 +5011,7 @@
         <v>115.57073600630167</v>
       </c>
     </row>
-    <row r="114" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>16</v>
       </c>
@@ -5042,7 +5046,7 @@
         <v>1919.8932886146356</v>
       </c>
     </row>
-    <row r="115" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>17</v>
       </c>
@@ -5077,7 +5081,7 @@
         <v>103.11709382182039</v>
       </c>
     </row>
-    <row r="116" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>18</v>
       </c>
@@ -5112,7 +5116,7 @@
         <v>62.974551917267533</v>
       </c>
     </row>
-    <row r="117" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>19</v>
       </c>
@@ -5147,7 +5151,7 @@
         <v>45.77474840351978</v>
       </c>
     </row>
-    <row r="118" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>20</v>
       </c>
@@ -5182,7 +5186,7 @@
         <v>33.315994070970369</v>
       </c>
     </row>
-    <row r="119" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>21</v>
       </c>
@@ -5217,7 +5221,7 @@
         <v>31.320622100687512</v>
       </c>
     </row>
-    <row r="120" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>22</v>
       </c>
@@ -5252,7 +5256,7 @@
         <v>24.517755297734634</v>
       </c>
     </row>
-    <row r="121" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>23</v>
       </c>
@@ -5287,7 +5291,7 @@
         <v>-4.3137702244226865</v>
       </c>
     </row>
-    <row r="122" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>2023</v>
       </c>
@@ -5322,7 +5326,7 @@
         <v>4.1699658104390247</v>
       </c>
     </row>
-    <row r="123" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>12</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>14.356352690923945</v>
       </c>
     </row>
-    <row r="124" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>13</v>
       </c>
@@ -5392,7 +5396,7 @@
         <v>-3.3610967339273268</v>
       </c>
     </row>
-    <row r="125" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>14</v>
       </c>
@@ -5427,7 +5431,7 @@
         <v>9.3732184262386617</v>
       </c>
     </row>
-    <row r="126" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>15</v>
       </c>
@@ -5462,7 +5466,7 @@
         <v>10.154759113499878</v>
       </c>
     </row>
-    <row r="127" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>16</v>
       </c>
@@ -5497,7 +5501,7 @@
         <v>19.491424675091551</v>
       </c>
     </row>
-    <row r="128" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>17</v>
       </c>
@@ -5532,7 +5536,7 @@
         <v>20.85802919534747</v>
       </c>
     </row>
-    <row r="129" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>18</v>
       </c>
@@ -5567,7 +5571,7 @@
         <v>14.050746234303402</v>
       </c>
     </row>
-    <row r="130" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>19</v>
       </c>
@@ -5602,7 +5606,7 @@
         <v>17.934588768948267</v>
       </c>
     </row>
-    <row r="131" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>20</v>
       </c>
@@ -5637,7 +5641,7 @@
         <v>23.818157743248115</v>
       </c>
     </row>
-    <row r="132" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>21</v>
       </c>
@@ -5672,7 +5676,7 @@
         <v>26.512655735497038</v>
       </c>
     </row>
-    <row r="133" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>22</v>
       </c>
@@ -5707,7 +5711,7 @@
         <v>27.634675140569609</v>
       </c>
     </row>
-    <row r="134" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>23</v>
       </c>
@@ -5742,7 +5746,7 @@
         <v>15.658434700802836</v>
       </c>
     </row>
-    <row r="135" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>2024</v>
       </c>
@@ -5777,7 +5781,7 @@
         <v>-16.678204100763683</v>
       </c>
     </row>
-    <row r="136" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>12</v>
       </c>
@@ -5812,7 +5816,7 @@
         <v>-27.506945165548135</v>
       </c>
     </row>
-    <row r="137" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>13</v>
       </c>
@@ -5847,7 +5851,7 @@
         <v>-19.428594487443352</v>
       </c>
     </row>
-    <row r="138" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>14</v>
       </c>
@@ -5882,7 +5886,7 @@
         <v>-24.462133389802045</v>
       </c>
     </row>
-    <row r="139" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>15</v>
       </c>
@@ -5917,7 +5921,7 @@
         <v>-36.01096677418051</v>
       </c>
     </row>
-    <row r="140" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>16</v>
       </c>
@@ -5952,7 +5956,7 @@
         <v>-37.815925337261824</v>
       </c>
     </row>
-    <row r="141" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>17</v>
       </c>
@@ -5987,7 +5991,7 @@
         <v>-26.590079561696879</v>
       </c>
     </row>
-    <row r="142" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>18</v>
       </c>
@@ -6022,7 +6026,7 @@
         <v>-30.727396759084215</v>
       </c>
     </row>
-    <row r="143" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>19</v>
       </c>
@@ -6057,7 +6061,7 @@
         <v>-28.934511623429803</v>
       </c>
     </row>
-    <row r="144" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>20</v>
       </c>
@@ -6092,7 +6096,7 @@
         <v>-33.970452222603022</v>
       </c>
     </row>
-    <row r="145" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>21</v>
       </c>
@@ -6127,7 +6131,7 @@
         <v>-40.652761984771544</v>
       </c>
     </row>
-    <row r="146" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>22</v>
       </c>
@@ -6162,7 +6166,7 @@
         <v>-25.809821695358405</v>
       </c>
     </row>
-    <row r="147" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>23</v>
       </c>
@@ -6197,7 +6201,7 @@
         <v>-19.986449286292153</v>
       </c>
     </row>
-    <row r="148" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>2025</v>
       </c>
@@ -6232,7 +6236,7 @@
         <v>-3.9234505626796867</v>
       </c>
     </row>
-    <row r="149" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>12</v>
       </c>
@@ -6267,7 +6271,7 @@
         <v>13.803575623435416</v>
       </c>
     </row>
-    <row r="150" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>13</v>
       </c>
@@ -6302,7 +6306,7 @@
         <v>4.9771982775025148</v>
       </c>
     </row>
-    <row r="151" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>14</v>
       </c>
@@ -6337,7 +6341,7 @@
         <v>16.935990503028584</v>
       </c>
     </row>
-    <row r="152" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>15</v>
       </c>
@@ -6372,531 +6376,632 @@
         <v>17.034002591007802</v>
       </c>
     </row>
-    <row r="153" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A153" s="2" t="s">
+    <row r="153" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A153" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B153" s="31">
+      <c r="B153" s="35">
         <v>-5.2679277078493181</v>
       </c>
-      <c r="C153" s="31">
+      <c r="C153" s="35">
         <v>-0.94953217593464201</v>
       </c>
-      <c r="D153" s="31">
+      <c r="D153" s="35">
         <v>14.91423342553977</v>
       </c>
-      <c r="E153" s="31">
+      <c r="E153" s="35">
         <v>-5.3591591102448488</v>
       </c>
-      <c r="F153" s="31">
+      <c r="F153" s="35">
         <v>39.97115383333545</v>
       </c>
-      <c r="G153" s="31">
+      <c r="G153" s="35">
         <v>31.363770046330263</v>
       </c>
-      <c r="H153" s="31">
+      <c r="H153" s="35">
         <v>12.913235956302049</v>
       </c>
-      <c r="I153" s="31">
+      <c r="I153" s="35">
         <v>35.77405662615061</v>
       </c>
-      <c r="J153" s="31">
+      <c r="J153" s="35">
         <v>13.806817679537353</v>
       </c>
-      <c r="K153" s="31">
+      <c r="K153" s="35">
         <v>12.762661226991501</v>
       </c>
     </row>
-    <row r="154" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A154" s="2" t="s">
+    <row r="154" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A154" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B154" s="31">
+      <c r="B154" s="35">
         <v>-3.2986546503694258</v>
       </c>
-      <c r="C154" s="31">
+      <c r="C154" s="35">
         <v>-11.652473909999895</v>
       </c>
-      <c r="D154" s="31">
+      <c r="D154" s="35">
         <v>2.151883958163836</v>
       </c>
-      <c r="E154" s="31">
+      <c r="E154" s="35">
         <v>-13.896454736534491</v>
       </c>
-      <c r="F154" s="31">
+      <c r="F154" s="35">
         <v>-2.1071413459955446</v>
       </c>
-      <c r="G154" s="31">
+      <c r="G154" s="35">
         <v>10.847372557013868</v>
       </c>
-      <c r="H154" s="31">
+      <c r="H154" s="35">
         <v>-6.5511822236301693</v>
       </c>
-      <c r="I154" s="31">
+      <c r="I154" s="35">
         <v>-37.029271807395936</v>
       </c>
-      <c r="J154" s="31">
+      <c r="J154" s="35">
         <v>-4.2821435906043366</v>
       </c>
-      <c r="K154" s="31">
+      <c r="K154" s="35">
         <v>-6.6642227594659325</v>
       </c>
     </row>
-    <row r="155" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A155" s="2" t="s">
+    <row r="155" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A155" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B155" s="31">
+      <c r="B155" s="35">
         <v>-11.566009139488308</v>
       </c>
-      <c r="C155" s="31">
+      <c r="C155" s="35">
         <v>-13.281074689464912</v>
       </c>
-      <c r="D155" s="31">
+      <c r="D155" s="35">
         <v>-4.2336294695575312</v>
       </c>
-      <c r="E155" s="31">
+      <c r="E155" s="35">
         <v>-9.4806034980343679</v>
       </c>
-      <c r="F155" s="31">
+      <c r="F155" s="35">
         <v>-2.1075346661576067</v>
       </c>
-      <c r="G155" s="31">
+      <c r="G155" s="35">
         <v>10.078211517706537</v>
       </c>
-      <c r="H155" s="31">
+      <c r="H155" s="35">
         <v>-2.6793583676416155</v>
       </c>
-      <c r="I155" s="31">
+      <c r="I155" s="35">
         <v>-15.982226558974066</v>
       </c>
-      <c r="J155" s="31">
+      <c r="J155" s="35">
         <v>7.4474347656583229</v>
       </c>
-      <c r="K155" s="31">
+      <c r="K155" s="35">
         <v>-9.3263616520678827</v>
       </c>
     </row>
-    <row r="156" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A156" s="2" t="s">
+    <row r="156" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A156" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B156" s="31">
+      <c r="B156" s="35">
         <v>-9.8008200724136749</v>
       </c>
-      <c r="C156" s="31">
+      <c r="C156" s="35">
         <v>-9.4333172711993818</v>
       </c>
-      <c r="D156" s="31">
+      <c r="D156" s="35">
         <v>0.36358840184989027</v>
       </c>
-      <c r="E156" s="31">
+      <c r="E156" s="35">
         <v>-0.92540851937937818</v>
       </c>
-      <c r="F156" s="31">
+      <c r="F156" s="35">
         <v>19.774818180034039</v>
       </c>
-      <c r="G156" s="31">
+      <c r="G156" s="35">
         <v>3.8693689362545136</v>
       </c>
-      <c r="H156" s="31">
+      <c r="H156" s="35">
         <v>-8.1744626097897353</v>
       </c>
-      <c r="I156" s="31">
+      <c r="I156" s="35">
         <v>8.7490768232779672</v>
       </c>
-      <c r="J156" s="31">
+      <c r="J156" s="35">
         <v>6.8120866139343983</v>
       </c>
-      <c r="K156" s="31">
+      <c r="K156" s="35">
         <v>-14.245350789958033</v>
       </c>
     </row>
-    <row r="157" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A157" s="2" t="s">
+    <row r="157" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A157" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="31">
+      <c r="B157" s="35">
         <v>-11.527414221791311</v>
       </c>
-      <c r="C157" s="31">
+      <c r="C157" s="35">
         <v>-5.6256359591605465</v>
       </c>
-      <c r="D157" s="31">
+      <c r="D157" s="35">
         <v>42.293349302950304</v>
       </c>
-      <c r="E157" s="31">
+      <c r="E157" s="35">
         <v>-0.76832426669124487</v>
       </c>
-      <c r="F157" s="31">
+      <c r="F157" s="35">
         <v>13.155962440532477</v>
       </c>
-      <c r="G157" s="31">
+      <c r="G157" s="35">
         <v>1.5952986159927018</v>
       </c>
-      <c r="H157" s="31">
+      <c r="H157" s="35">
         <v>-8.9525564715623123</v>
       </c>
-      <c r="I157" s="31">
+      <c r="I157" s="35">
         <v>27.221329819574393</v>
       </c>
-      <c r="J157" s="31">
+      <c r="J157" s="35">
         <v>2.3003020895056236</v>
       </c>
-      <c r="K157" s="31">
+      <c r="K157" s="35">
         <v>-13.588958706756294</v>
       </c>
     </row>
-    <row r="158" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A158" s="2" t="s">
+    <row r="158" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A158" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B158" s="31">
+      <c r="B158" s="35">
         <v>-5.8618528097964084</v>
       </c>
-      <c r="C158" s="31">
+      <c r="C158" s="35">
         <v>-4.200667120847223</v>
       </c>
-      <c r="D158" s="31">
+      <c r="D158" s="35">
         <v>74.103184451131909</v>
       </c>
-      <c r="E158" s="31">
+      <c r="E158" s="35">
         <v>-1.5863746929946188</v>
       </c>
-      <c r="F158" s="31">
+      <c r="F158" s="35">
         <v>11.297860938932525</v>
       </c>
-      <c r="G158" s="31">
+      <c r="G158" s="35">
         <v>2.0567991335282532</v>
       </c>
-      <c r="H158" s="31">
+      <c r="H158" s="35">
         <v>-1.5641044156876949</v>
       </c>
-      <c r="I158" s="31">
+      <c r="I158" s="35">
         <v>-26.184698079517808</v>
       </c>
-      <c r="J158" s="31">
+      <c r="J158" s="35">
         <v>0.7745959307488004</v>
       </c>
-      <c r="K158" s="31">
+      <c r="K158" s="35">
         <v>-5.9948136103240124</v>
       </c>
     </row>
-    <row r="159" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A159" s="2" t="s">
+    <row r="159" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A159" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B159" s="31">
+      <c r="B159" s="35">
         <v>3.7322578622188685</v>
       </c>
-      <c r="C159" s="31">
+      <c r="C159" s="35">
         <v>-3.418901828971832</v>
       </c>
-      <c r="D159" s="31">
+      <c r="D159" s="35">
         <v>66.786442236362802</v>
       </c>
-      <c r="E159" s="31">
+      <c r="E159" s="35">
         <v>-0.23592275475184943</v>
       </c>
-      <c r="F159" s="31">
+      <c r="F159" s="35">
         <v>0.45167282749771775</v>
       </c>
-      <c r="G159" s="31">
+      <c r="G159" s="35">
         <v>3.3968381850322471</v>
       </c>
-      <c r="H159" s="31">
+      <c r="H159" s="35">
         <v>4.6097595539379199</v>
       </c>
-      <c r="I159" s="31">
+      <c r="I159" s="35">
         <v>-27.168516587815429</v>
       </c>
-      <c r="J159" s="31">
+      <c r="J159" s="35">
         <v>11.008508868558909</v>
       </c>
-      <c r="K159" s="31">
+      <c r="K159" s="35">
         <v>-19.14810650609612</v>
       </c>
     </row>
-    <row r="160" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A160" s="2" t="s">
+    <row r="160" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A160" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B160" s="31">
+      <c r="B160" s="35">
         <v>2.0858642426762053</v>
       </c>
-      <c r="C160" s="31">
+      <c r="C160" s="35">
         <v>-4.8233816782494721E-2</v>
       </c>
-      <c r="D160" s="31">
+      <c r="D160" s="35">
         <v>49.781527723605222</v>
       </c>
-      <c r="E160" s="31">
+      <c r="E160" s="35">
         <v>-4.8807095410255741</v>
       </c>
-      <c r="F160" s="31">
+      <c r="F160" s="35">
         <v>1.2355301806196151</v>
       </c>
-      <c r="G160" s="31">
+      <c r="G160" s="35">
         <v>-4.4032604527998176</v>
       </c>
-      <c r="H160" s="31">
+      <c r="H160" s="35">
         <v>-6.3443391169110903</v>
       </c>
-      <c r="I160" s="31">
+      <c r="I160" s="35">
         <v>-13.622710048909681</v>
       </c>
-      <c r="J160" s="31">
+      <c r="J160" s="35">
         <v>0.19955457853402248</v>
       </c>
-      <c r="K160" s="31">
+      <c r="K160" s="35">
         <v>-17.575346128292491</v>
       </c>
     </row>
-    <row r="161" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A161" s="4">
+    <row r="161" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A161" s="36">
         <v>2026</v>
       </c>
-      <c r="B161" s="31"/>
-      <c r="C161" s="31"/>
-      <c r="D161" s="31"/>
-      <c r="E161" s="31"/>
-      <c r="F161" s="31"/>
-      <c r="G161" s="31"/>
-      <c r="H161" s="31"/>
-      <c r="I161" s="31"/>
-      <c r="J161" s="31"/>
-      <c r="K161" s="31"/>
-    </row>
-    <row r="162" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A162" s="2" t="s">
+      <c r="B161" s="35"/>
+      <c r="C161" s="35"/>
+      <c r="D161" s="35"/>
+      <c r="E161" s="35"/>
+      <c r="F161" s="35"/>
+      <c r="G161" s="35"/>
+      <c r="H161" s="35"/>
+      <c r="I161" s="35"/>
+      <c r="J161" s="35"/>
+      <c r="K161" s="35"/>
+    </row>
+    <row r="162" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A162" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B162" s="31">
+      <c r="B162" s="35">
         <v>5.8152767443154119</v>
       </c>
-      <c r="C162" s="31">
+      <c r="C162" s="35">
         <v>2.4498586865609795</v>
       </c>
-      <c r="D162" s="31">
+      <c r="D162" s="35">
         <v>91.524913635223839</v>
       </c>
-      <c r="E162" s="31">
+      <c r="E162" s="35">
         <v>-4.1160047797977439</v>
       </c>
-      <c r="F162" s="31">
+      <c r="F162" s="35">
         <v>-3.1818121272530031</v>
       </c>
-      <c r="G162" s="31">
+      <c r="G162" s="35">
         <v>-2.8218505811684613</v>
       </c>
-      <c r="H162" s="31">
+      <c r="H162" s="35">
         <v>-3.5425625618972112</v>
       </c>
-      <c r="I162" s="31">
+      <c r="I162" s="35">
         <v>-17.840478586072539</v>
       </c>
-      <c r="J162" s="31">
+      <c r="J162" s="35">
         <v>14.857863616393786</v>
       </c>
-      <c r="K162" s="31">
+      <c r="K162" s="35">
         <v>-10.78053091076595</v>
       </c>
     </row>
-    <row r="163" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A163" s="2" t="s">
+    <row r="163" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A163" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B163" s="31">
+      <c r="B163" s="35">
         <v>9.4242627999750805</v>
       </c>
-      <c r="C163" s="31">
+      <c r="C163" s="35">
         <v>15.087059446122474</v>
       </c>
-      <c r="D163" s="31">
+      <c r="D163" s="35">
         <v>82.226334583928832</v>
       </c>
-      <c r="E163" s="31">
+      <c r="E163" s="35">
         <v>-2.5256476319319376</v>
       </c>
-      <c r="F163" s="31">
+      <c r="F163" s="35">
         <v>-29.217457484690247</v>
       </c>
-      <c r="G163" s="31">
+      <c r="G163" s="35">
         <v>2.5841162234958137</v>
       </c>
-      <c r="H163" s="31">
+      <c r="H163" s="35">
         <v>-4.8083007609946771</v>
       </c>
-      <c r="I163" s="31">
+      <c r="I163" s="35">
         <v>-10.605643197174896</v>
       </c>
-      <c r="J163" s="31">
+      <c r="J163" s="35">
         <v>12.971969168889652</v>
       </c>
-      <c r="K163" s="31">
+      <c r="K163" s="35">
         <v>-11.877993018855948</v>
       </c>
     </row>
-    <row r="164" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A164" s="2" t="s">
+    <row r="164" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A164" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B164" s="31">
+      <c r="B164" s="35">
         <v>-5.7864076956359201</v>
       </c>
-      <c r="C164" s="31">
+      <c r="C164" s="35">
         <v>13.03120821205621</v>
       </c>
-      <c r="D164" s="31">
+      <c r="D164" s="35">
         <v>49.586459065204977</v>
       </c>
-      <c r="E164" s="31">
+      <c r="E164" s="35">
         <v>-12.647514694402096</v>
       </c>
-      <c r="F164" s="31">
+      <c r="F164" s="35">
         <v>-7.9963659075643516</v>
       </c>
-      <c r="G164" s="31">
+      <c r="G164" s="35">
         <v>-16.261321850888866</v>
       </c>
-      <c r="H164" s="31">
+      <c r="H164" s="35">
         <v>-12.850029289597153</v>
       </c>
-      <c r="I164" s="31">
+      <c r="I164" s="35">
         <v>-26.070788048308525</v>
       </c>
-      <c r="J164" s="31">
+      <c r="J164" s="35">
         <v>2.8436331589110075</v>
       </c>
-      <c r="K164" s="31">
+      <c r="K164" s="35">
         <v>-19.44505267367812</v>
       </c>
     </row>
-    <row r="165" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A165" s="2" t="s">
+    <row r="165" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A165" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B165" s="31">
+      <c r="B165" s="35">
         <v>2.0235334275078953</v>
       </c>
-      <c r="C165" s="31">
+      <c r="C165" s="35">
         <v>20.11965277380332</v>
       </c>
-      <c r="D165" s="31">
+      <c r="D165" s="35">
         <v>84.989757124455181</v>
       </c>
-      <c r="E165" s="31">
+      <c r="E165" s="35">
         <v>-3.037364617633953</v>
       </c>
-      <c r="F165" s="31">
+      <c r="F165" s="35">
         <v>-22.882113478593769</v>
       </c>
-      <c r="G165" s="31">
+      <c r="G165" s="35">
         <v>-8.4969622772096738</v>
       </c>
-      <c r="H165" s="31">
+      <c r="H165" s="35">
         <v>-3.3087069110345202</v>
       </c>
-      <c r="I165" s="31">
+      <c r="I165" s="35">
         <v>-5.8094340275673062</v>
       </c>
-      <c r="J165" s="31">
+      <c r="J165" s="35">
         <v>8.3484741385152041</v>
       </c>
-      <c r="K165" s="31">
+      <c r="K165" s="35">
         <v>-10.553779332907276</v>
       </c>
     </row>
-    <row r="166" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A166" s="23" t="s">
+    <row r="166" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A166" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B166" s="30">
+      <c r="B166" s="35">
         <v>21.785776842501512</v>
       </c>
-      <c r="C166" s="30">
+      <c r="C166" s="35">
         <v>33.502499828042431</v>
       </c>
-      <c r="D166" s="30">
+      <c r="D166" s="35">
         <v>111.53185904991921</v>
       </c>
-      <c r="E166" s="30">
+      <c r="E166" s="35">
         <v>9.2022268064088095</v>
       </c>
-      <c r="F166" s="30">
+      <c r="F166" s="35">
         <v>-17.530881472698223</v>
       </c>
-      <c r="G166" s="30">
+      <c r="G166" s="35">
         <v>5.748044330821922</v>
       </c>
-      <c r="H166" s="30">
+      <c r="H166" s="35">
         <v>-8.362704000130039</v>
       </c>
-      <c r="I166" s="30">
+      <c r="I166" s="35">
         <v>-7.9607564480824511</v>
       </c>
-      <c r="J166" s="30">
+      <c r="J166" s="35">
         <v>17.552686765482694</v>
       </c>
-      <c r="K166" s="30">
+      <c r="K166" s="35">
         <v>-2.0735552481443986</v>
       </c>
     </row>
-    <row r="167" spans="1:11" s="2" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A167" s="24" t="s">
+    <row r="167" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A167" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B167" s="30">
+        <v>-3.6078468416862131</v>
+      </c>
+      <c r="C167" s="30">
+        <v>24.151078709736208</v>
+      </c>
+      <c r="D167" s="30">
+        <v>143.44835271514577</v>
+      </c>
+      <c r="E167" s="30">
+        <v>-4.4299175203395214</v>
+      </c>
+      <c r="F167" s="30">
+        <v>-13.528216791591808</v>
+      </c>
+      <c r="G167" s="30">
+        <v>-10.689152894469656</v>
+      </c>
+      <c r="H167" s="30">
+        <v>-19.841171670565348</v>
+      </c>
+      <c r="I167" s="30">
+        <v>-3.9629145947990496</v>
+      </c>
+      <c r="J167" s="30">
+        <v>-4.7313458379755646</v>
+      </c>
+      <c r="K167" s="30">
+        <v>-13.758355651091215</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A168" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B167" s="25"/>
-      <c r="C167" s="25"/>
-      <c r="D167" s="25"/>
-      <c r="E167" s="21"/>
-      <c r="F167" s="21"/>
-      <c r="G167" s="21"/>
-      <c r="H167" s="21"/>
-      <c r="I167" s="21"/>
-      <c r="J167" s="21"/>
-      <c r="K167" s="21"/>
-    </row>
-    <row r="168" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="39" t="s">
+      <c r="B168" s="25"/>
+      <c r="C168" s="25"/>
+      <c r="D168" s="25"/>
+      <c r="E168" s="21"/>
+      <c r="F168" s="21"/>
+      <c r="G168" s="21"/>
+      <c r="H168" s="21"/>
+      <c r="I168" s="21"/>
+      <c r="J168" s="21"/>
+      <c r="K168" s="21"/>
+    </row>
+    <row r="169" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="B168" s="39"/>
-      <c r="C168" s="39"/>
-      <c r="D168" s="39"/>
-      <c r="E168" s="39"/>
-      <c r="F168" s="39"/>
-      <c r="G168" s="39"/>
-      <c r="H168" s="39"/>
-      <c r="I168" s="39"/>
-      <c r="J168" s="39"/>
-      <c r="K168" s="39"/>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169" s="39"/>
-      <c r="B169" s="39"/>
-      <c r="C169" s="39"/>
-      <c r="D169" s="39"/>
-      <c r="E169" s="39"/>
-      <c r="F169" s="39"/>
-      <c r="G169" s="39"/>
-      <c r="H169" s="39"/>
-      <c r="I169" s="39"/>
-      <c r="J169" s="39"/>
-      <c r="K169" s="39"/>
-    </row>
-    <row r="177" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="178" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="179" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="180" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="181" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="182" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="B169" s="42"/>
+      <c r="C169" s="42"/>
+      <c r="D169" s="42"/>
+      <c r="E169" s="42"/>
+      <c r="F169" s="42"/>
+      <c r="G169" s="42"/>
+      <c r="H169" s="42"/>
+      <c r="I169" s="42"/>
+      <c r="J169" s="42"/>
+      <c r="K169" s="42"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A170" s="42"/>
+      <c r="B170" s="42"/>
+      <c r="C170" s="42"/>
+      <c r="D170" s="42"/>
+      <c r="E170" s="42"/>
+      <c r="F170" s="42"/>
+      <c r="G170" s="42"/>
+      <c r="H170" s="42"/>
+      <c r="I170" s="42"/>
+      <c r="J170" s="42"/>
+      <c r="K170" s="42"/>
+    </row>
+    <row r="178" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="K178" s="1"/>
+    </row>
+    <row r="179" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+      <c r="J179" s="1"/>
+      <c r="K179" s="1"/>
+    </row>
+    <row r="180" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+      <c r="G180" s="1"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+      <c r="J180" s="1"/>
+      <c r="K180" s="1"/>
+    </row>
+    <row r="181" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+      <c r="G181" s="1"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="K181" s="1"/>
+    </row>
+    <row r="182" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="K182" s="1"/>
+    </row>
+    <row r="183" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="1"/>
+      <c r="G183" s="1"/>
+      <c r="H183" s="1"/>
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+      <c r="K183" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A168:K169"/>
+    <mergeCell ref="A169:K170"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6909,22 +7014,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.09765625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="48.59765625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="10.59765625" style="6"/>
+    <col min="1" max="1" width="35.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="48.625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="10.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="41"/>
-    </row>
-    <row r="2" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="44"/>
+    </row>
+    <row r="2" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
@@ -6932,7 +7037,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -6940,7 +7045,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>30</v>
       </c>
@@ -6948,7 +7053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
@@ -6956,7 +7061,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="32" t="s">
         <v>34</v>
       </c>
@@ -6964,7 +7069,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>35</v>
       </c>
@@ -6972,7 +7077,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>37</v>
       </c>
@@ -6980,7 +7085,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
@@ -6988,7 +7093,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>39</v>
       </c>
@@ -6999,7 +7104,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>41</v>
       </c>
@@ -7007,7 +7112,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>43</v>
       </c>
@@ -7015,7 +7120,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>50</v>
       </c>
@@ -7023,7 +7128,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>45</v>
       </c>
@@ -7031,33 +7136,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="42" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="48" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
-      <c r="B16" s="46"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="43"/>
-      <c r="B17" s="46"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="43"/>
-      <c r="B18" s="46"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="43"/>
-      <c r="B19" s="46"/>
-    </row>
-    <row r="20" spans="1:2" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="44"/>
-      <c r="B20" s="47"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="46"/>
+      <c r="B16" s="49"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="46"/>
+      <c r="B17" s="49"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="46"/>
+      <c r="B18" s="49"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="46"/>
+      <c r="B19" s="49"/>
+    </row>
+    <row r="20" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="47"/>
+      <c r="B20" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="3">
